--- a/data/dividends_info_20260619.xlsx
+++ b/data/dividends_info_20260619.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>67.75</v>
+        <v>67.91999816894531</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1328413284132841</v>
+        <v>0.1325088374945661</v>
       </c>
       <c r="J2" t="n">
         <v>269</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.69999694824219</v>
+        <v>65.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.065449060144482</v>
+        <v>1.068702290076336</v>
       </c>
       <c r="J3" t="n">
         <v>248</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.300000190734863</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6451612770908873</v>
+        <v>0.6550218449725329</v>
       </c>
       <c r="J4" t="n">
         <v>178</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.851063831945845</v>
       </c>
       <c r="J5" t="n">
         <v>178</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>67.75</v>
+        <v>67.91999816894531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1328413284132841</v>
+        <v>0.1325088374945661</v>
       </c>
       <c r="J6" t="n">
         <v>178</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.065000057220459</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I7" t="n">
-        <v>3.728813455997861</v>
+        <v>3.68421067761643</v>
       </c>
       <c r="J7" t="n">
         <v>157</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.6299991607666</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>1.248266345242109</v>
+        <v>1.247689499146453</v>
       </c>
       <c r="J8" t="n">
         <v>157</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.940000057220459</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="I9" t="n">
-        <v>3.367003334568775</v>
+        <v>3.311258299058689</v>
       </c>
       <c r="J9" t="n">
         <v>150</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.349999904632568</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8163265412042129</v>
+        <v>0.8333333554091283</v>
       </c>
       <c r="J10" t="n">
         <v>122</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.851063831945845</v>
       </c>
       <c r="J11" t="n">
         <v>122</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.860000133514404</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8532423013788162</v>
+        <v>0.8417508336421938</v>
       </c>
       <c r="J12" t="n">
         <v>108</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J13" t="n">
         <v>101</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.6299991607666</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="I14" t="n">
-        <v>1.248266345242109</v>
+        <v>1.247689499146453</v>
       </c>
       <c r="J14" t="n">
         <v>94</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>67.75</v>
+        <v>67.91999816894531</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1328413284132841</v>
+        <v>0.1325088374945661</v>
       </c>
       <c r="J15" t="n">
         <v>94</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.900000095367432</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="I16" t="n">
-        <v>5.08474568052218</v>
+        <v>5.016722392025687</v>
       </c>
       <c r="J16" t="n">
         <v>87</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.851063831945845</v>
       </c>
       <c r="J17" t="n">
         <v>66</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J18" t="n">
         <v>45</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.440000057220459</v>
+        <v>5.489999771118164</v>
       </c>
       <c r="I19" t="n">
-        <v>4.595588186955577</v>
+        <v>4.553734251779063</v>
       </c>
       <c r="J19" t="n">
         <v>38</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.199999809265137</v>
+        <v>4.190000057220459</v>
       </c>
       <c r="I20" t="n">
-        <v>3.333333484710216</v>
+        <v>3.34128873718614</v>
       </c>
       <c r="J20" t="n">
         <v>31</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.914999961853027</v>
+        <v>9.939000129699707</v>
       </c>
       <c r="I21" t="n">
-        <v>2.622289470502512</v>
+        <v>2.615957305635487</v>
       </c>
       <c r="J21" t="n">
         <v>31</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.5600004196167</v>
+        <v>14.73999977111816</v>
       </c>
       <c r="I22" t="n">
-        <v>4.120879002116096</v>
+        <v>4.070556372569635</v>
       </c>
       <c r="J22" t="n">
         <v>31</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.694000005722046</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="I23" t="n">
-        <v>5.955603672420618</v>
+        <v>6.010928820786296</v>
       </c>
       <c r="J23" t="n">
         <v>31</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.851063831945845</v>
       </c>
       <c r="J24" t="n">
         <v>31</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.400000095367432</v>
+        <v>6.364999771118164</v>
       </c>
       <c r="I25" t="n">
-        <v>1.562499976716936</v>
+        <v>1.571091965372257</v>
       </c>
       <c r="J25" t="n">
         <v>31</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.39999961853027</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>2.04347830323506</v>
+        <v>2.02150533488478</v>
       </c>
       <c r="J26" t="n">
         <v>31</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.051282084722308</v>
       </c>
       <c r="J27" t="n">
         <v>24</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>8.899999618530273</v>
+        <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5617977768886342</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J28" t="n">
         <v>24</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.720000028610229</v>
+        <v>2.779999971389771</v>
       </c>
       <c r="I29" t="n">
-        <v>5.514705824346692</v>
+        <v>5.395683508766814</v>
       </c>
       <c r="J29" t="n">
         <v>24</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.160000085830688</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I30" t="n">
-        <v>3.935185028814982</v>
+        <v>3.971962422114281</v>
       </c>
       <c r="J30" t="n">
         <v>17</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>37.25</v>
+        <v>36.54999923706055</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4026845637583892</v>
+        <v>0.4103967253928277</v>
       </c>
       <c r="J32" t="n">
         <v>17</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.099999904632568</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I33" t="n">
-        <v>0.784313740156468</v>
+        <v>0.7766990147433418</v>
       </c>
       <c r="J33" t="n">
         <v>10</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.73999977111816</v>
+        <v>23</v>
       </c>
       <c r="I34" t="n">
-        <v>1.099384355832415</v>
+        <v>1.08695652173913</v>
       </c>
       <c r="J34" t="n">
         <v>3</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29.75</v>
+        <v>29.85000038146973</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6554621848739496</v>
+        <v>0.6532663233098384</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.860000014305115</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="I36" t="n">
-        <v>1.774193534741913</v>
+        <v>1.764705877853063</v>
       </c>
       <c r="J36" t="n">
         <v>3</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.565000057220459</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="I37" t="n">
-        <v>5.211141006615654</v>
+        <v>5.234657075755654</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.796000003814697</v>
+        <v>3.803999900817871</v>
       </c>
       <c r="I38" t="n">
-        <v>4.214963114836984</v>
+        <v>4.20609895298892</v>
       </c>
       <c r="J38" t="n">
         <v>3</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.644000053405762</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="I39" t="n">
-        <v>5.24205738277002</v>
+        <v>5.230188491022776</v>
       </c>
       <c r="J39" t="n">
         <v>3</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>53.04000091552734</v>
+        <v>52.65999984741211</v>
       </c>
       <c r="I40" t="n">
-        <v>1.187782784927458</v>
+        <v>1.196353972323379</v>
       </c>
       <c r="J40" t="n">
         <v>3</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.380000114440918</v>
+        <v>6.420000076293945</v>
       </c>
       <c r="I41" t="n">
-        <v>2.194357327409989</v>
+        <v>2.180685332340641</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18</v>
+        <v>18.25</v>
       </c>
       <c r="I42" t="n">
-        <v>4.333333333333334</v>
+        <v>4.273972602739726</v>
       </c>
       <c r="J42" t="n">
         <v>3</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>29.17000007629395</v>
+        <v>28.97999954223633</v>
       </c>
       <c r="I43" t="n">
-        <v>2.91395268349959</v>
+        <v>2.933057327213495</v>
       </c>
       <c r="J43" t="n">
         <v>3</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>67.75</v>
+        <v>67.91999816894531</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1328413284132841</v>
+        <v>0.1325088374945661</v>
       </c>
       <c r="J44" t="n">
         <v>3</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.559999942779541</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6410256645383223</v>
+        <v>0.6451613101701217</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.392000198364258</v>
+        <v>6.443999767303467</v>
       </c>
       <c r="I46" t="n">
-        <v>2.836357859413013</v>
+        <v>2.813469996071495</v>
       </c>
       <c r="J46" t="n">
         <v>3</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.020000457763672</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="I47" t="n">
-        <v>2.882483224002649</v>
+        <v>2.860285980589108</v>
       </c>
       <c r="J47" t="n">
         <v>3</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.28499984741211</v>
+        <v>10.34000015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>2.693242626247566</v>
+        <v>2.678916788320091</v>
       </c>
       <c r="J48" t="n">
         <v>3</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.004999995231628</v>
+        <v>1.024999976158142</v>
       </c>
       <c r="I49" t="n">
-        <v>1.34328358846296</v>
+        <v>1.31707320136729</v>
       </c>
       <c r="J49" t="n">
         <v>-4</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.101999998092651</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="I50" t="n">
-        <v>3.546099292960557</v>
+        <v>3.559870649044061</v>
       </c>
       <c r="J50" t="n">
         <v>-4</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.629999995231628</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="I51" t="n">
-        <v>1.47239264234412</v>
+        <v>1.518987300514011</v>
       </c>
       <c r="J51" t="n">
         <v>-4</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.970000028610229</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="I52" t="n">
-        <v>5.38720533531004</v>
+        <v>5.36912748241343</v>
       </c>
       <c r="J52" t="n">
         <v>-11</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8650000095367432</v>
+        <v>0.8550000190734863</v>
       </c>
       <c r="I53" t="n">
-        <v>2.890173378540068</v>
+        <v>2.923976542958566</v>
       </c>
       <c r="J53" t="n">
         <v>-11</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.04999923706055</v>
+        <v>27</v>
       </c>
       <c r="I54" t="n">
-        <v>4.103512130526112</v>
+        <v>4.111111111111112</v>
       </c>
       <c r="J54" t="n">
         <v>-15</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9179999828338623</v>
+        <v>0.9039999842643738</v>
       </c>
       <c r="I55" t="n">
-        <v>3.267973917318617</v>
+        <v>3.318584128561946</v>
       </c>
       <c r="J55" t="n">
         <v>-18</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4715000092983246</v>
+        <v>0.4704999923706055</v>
       </c>
       <c r="I56" t="n">
-        <v>4.87804868428912</v>
+        <v>4.888416657376534</v>
       </c>
       <c r="J56" t="n">
         <v>-18</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.29999923706055</v>
+        <v>19.39999961853027</v>
       </c>
       <c r="I57" t="n">
-        <v>3.108808413048321</v>
+        <v>3.092783565969242</v>
       </c>
       <c r="J57" t="n">
         <v>-18</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.260000228881836</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I58" t="n">
-        <v>2.159827160437882</v>
+        <v>2.127659660812527</v>
       </c>
       <c r="J58" t="n">
         <v>-18</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.394999980926514</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="I59" t="n">
-        <v>7.515657679895529</v>
+        <v>7.468879402050181</v>
       </c>
       <c r="J59" t="n">
         <v>-25</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.149999618530273</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I60" t="n">
-        <v>3.68098176738443</v>
+        <v>3.614457748264686</v>
       </c>
       <c r="J60" t="n">
         <v>-25</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.8799991607666</v>
+        <v>17</v>
       </c>
       <c r="I61" t="n">
-        <v>1.481042727662353</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="J61" t="n">
         <v>-25</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.039999961853027</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7425742644373664</v>
+        <v>0.7556675008514305</v>
       </c>
       <c r="J62" t="n">
         <v>-25</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.64999961853027</v>
+        <v>12.75</v>
       </c>
       <c r="I64" t="n">
-        <v>4.584980375417487</v>
+        <v>4.549019607843137</v>
       </c>
       <c r="J64" t="n">
         <v>-25</v>
